--- a/data/checkpoints/d4_end_limits.xlsx
+++ b/data/checkpoints/d4_end_limits.xlsx
@@ -504,7 +504,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>(4일차 기준 결과) proposed_limit = PuLP 3.3.2 해(1달러 내림 — 합계 ≤ TotalCap) — Day5 d5_start limit_usd 원천</t>
+          <t>(4일차 기준 결과) proposed_limit = PuLP 3.3.2 해(1달러 내림 — 합계 ≤ TotalCap) — 5일차 시작 파일 d5_start.csv의 limit_usd와 같은 값</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32.7109375" customWidth="1" min="1" max="1"/>
@@ -15309,14 +15309,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>② EL 예산 끔</t>
+          <t>카드 ③ 국가 캡 끄기(CtryCap 모두 1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3135799.49</v>
+        <v>3137233.77</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1434.28</v>
       </c>
       <c r="D3" t="n">
         <v>2600000</v>
@@ -15325,19 +15325,24 @@
         <v>2600000</v>
       </c>
       <c r="F3" t="n">
-        <v>2562.11</v>
+        <v>2560.06</v>
       </c>
       <c r="G3" t="n">
         <v>300000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>total_cap · ctry_NGA</t>
+          <t>total_cap</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>total_cap 0.6723; ctry_NGA 1.3959</t>
+          <t>total_cap 0.6723</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>POL(1) · NGA(1)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -15349,14 +15354,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>③ 국가 한도 끔</t>
+          <t>카드 ④ B등급 비중 끄기(ShareCap_B 0.3 → 1)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3137233.77</v>
+        <v>3135799.49</v>
       </c>
       <c r="C4" t="n">
-        <v>1434.28</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>2600000</v>
@@ -15365,24 +15370,19 @@
         <v>2600000</v>
       </c>
       <c r="F4" t="n">
-        <v>2560.06</v>
+        <v>2562.11</v>
       </c>
       <c r="G4" t="n">
         <v>300000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>total_cap</t>
+          <t>total_cap · ctry_NGA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>total_cap 0.6723</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>POL(1) · NGA(1)</t>
+          <t>total_cap 0.6723; ctry_NGA 1.3959</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -15394,14 +15394,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>④ B등급 비중 끔</t>
+          <t>카드 ② EL 예산 조이기(Alpha 0.03 → 0.0002)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3135799.49</v>
+        <v>3133961.95</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-1837.54</v>
       </c>
       <c r="D5" t="n">
         <v>2600000</v>
@@ -15410,19 +15410,24 @@
         <v>2600000</v>
       </c>
       <c r="F5" t="n">
-        <v>2562.11</v>
+        <v>2000</v>
       </c>
       <c r="G5" t="n">
-        <v>300000</v>
+        <v>2000</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>total_cap · ctry_NGA</t>
+          <t>total_cap · el_budget · ctry_NGA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>total_cap 0.6723; ctry_NGA 1.3959</t>
+          <t>total_cap 0.6654; el_budget 3.269; ctry_NGA 1.4024</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>DEU(3) · USA(2) · JPN(2) · GBR(2)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -15434,40 +15439,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>α 3% → 0.02%(EL 예산 2천 달러)</t>
+          <t>카드 ① 총액 비율 올리기(TotalCapShare 0.7 → 0.8)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3133961.95</v>
+        <v>3338544.32</v>
       </c>
       <c r="C6" t="n">
-        <v>-1837.54</v>
+        <v>202744.82</v>
       </c>
       <c r="D6" t="n">
-        <v>2600000</v>
+        <v>2900000</v>
       </c>
       <c r="E6" t="n">
-        <v>2600000</v>
+        <v>2900000</v>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>3074.61</v>
       </c>
       <c r="G6" t="n">
-        <v>2000</v>
+        <v>300000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>total_cap · el_budget · ctry_NGA</t>
+          <t>total_cap</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>total_cap 0.6654; el_budget 3.269; ctry_NGA 1.4024</t>
+          <t>total_cap 0.6658</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DEU(3) · USA(2) · JPN(2) · GBR(2)</t>
+          <t>CHN(2) · NLD(1) · IDN(1) · TWN(1)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -15479,88 +15484,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TotalCapShare 70% → 80%</t>
+          <t>카드 ⑤ 등급 규칙을 분위수로(grade_quantile)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3338544.32</v>
+        <v>2496069.91</v>
       </c>
       <c r="C7" t="n">
-        <v>202744.82</v>
+        <v>-639729.58</v>
       </c>
       <c r="D7" t="n">
-        <v>2900000</v>
+        <v>2300000</v>
       </c>
       <c r="E7" t="n">
-        <v>2900000</v>
+        <v>2119579.53</v>
       </c>
       <c r="F7" t="n">
-        <v>3074.61</v>
+        <v>10238.59</v>
       </c>
       <c r="G7" t="n">
         <v>300000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>total_cap</t>
+          <t>ctry_NGA · b_share</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>total_cap 0.6658</t>
+          <t>ctry_NGA 1.038; b_share 1.0055</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CHN(2) · NLD(1) · IDN(1) · TWN(1)</t>
+          <t>DEU(5) · USA(4) · JPN(4) · VNM(3)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>{"S": 127, "C": 18, "B": 3, "A": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GradeRule = quantile(🔵)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2496069.91</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-639729.58</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2119579.53</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10238.59</v>
-      </c>
-      <c r="G8" t="n">
-        <v>300000</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ctry_NGA · b_share</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ctry_NGA 1.038; b_share 1.0055</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>DEU(5) · USA(4) · JPN(4) · VNM(3)</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>{"B": 53, "A": 52, "C": 23, "S": 22}</t>
         </is>
